--- a/test_reconciliation.xlsx
+++ b/test_reconciliation.xlsx
@@ -9,7 +9,6 @@
   <sheets>
     <sheet name="Bank_Statement" sheetId="1" state="visible" r:id="rId1"/>
     <sheet name="Internal_Ledger" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="ML_Reconciliation_Results" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -415,13 +414,13 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C5"/>
+  <dimension ref="A1:D101"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>Date</t>
+          <t>Posting Date</t>
         </is>
       </c>
       <c r="B1" t="inlineStr">
@@ -432,67 +431,2012 @@
       <c r="C1" t="inlineStr">
         <is>
           <t>Amount</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>Bank Reference</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2023-10-01</t>
+          <t>2024-03-31</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>ACH Transfer - Vendor A</t>
+          <t>WIRE OUT FABRIKAM LOGISTIC INV-2073</t>
         </is>
       </c>
       <c r="C2" t="n">
-        <v>-1500</v>
+        <v>-8070.83</v>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>BK213167</t>
+        </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2023-10-02</t>
+          <t>2024-02-20</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>POS Debit - Coffee Shop</t>
+          <t>POS DEBIT ADATUM CLEANING</t>
         </is>
       </c>
       <c r="C3" t="n">
-        <v>-4.5</v>
+        <v>-8305.99</v>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>BK161843</t>
+        </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2023-10-05</t>
+          <t>2024-03-10</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Wire Transfer IN - Client B</t>
+          <t>WIRE OUT WIDE WORLD IMP</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>5000</v>
+        <v>-371.58</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>BK821497</t>
+        </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2023-10-10</t>
+          <t>2024-04-15</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Fee - Monthly Maintenance</t>
+          <t>CARD PURCHASE LITWARE HOST</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>-15</v>
+        <v>-5965</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>BK218454</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>2024-04-01</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>ACH DEBIT GRAPHIC DESIGN</t>
+        </is>
+      </c>
+      <c r="C6" t="n">
+        <v>-1729.68</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>BK339613</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>2024-02-08</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>ACH DEBIT CONTOSO SUPPLIES</t>
+        </is>
+      </c>
+      <c r="C7" t="n">
+        <v>-2820.39</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>BK747772</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>2024-04-14</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>CARD PURCHASE TAILSPIN TRVL</t>
+        </is>
+      </c>
+      <c r="C8" t="n">
+        <v>-7177.19</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>BK216224</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>2024-01-05</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>CARD PURCHASE LITWARE HOST INV-2089</t>
+        </is>
+      </c>
+      <c r="C9" t="n">
+        <v>-4537.48</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>BK210820</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>2024-01-15</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>ACH DEBIT CONTOSO SUPPLIES INV-2054</t>
+        </is>
+      </c>
+      <c r="C10" t="n">
+        <v>-5645.11</v>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>BK817711</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>2024-01-03</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>ACH DEBIT GRAPHIC DESIGN</t>
+        </is>
+      </c>
+      <c r="C11" t="n">
+        <v>-5661.73</v>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>BK813720</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>2024-03-30</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>WIRE OUT FABRIKAM LOGISTIC BATCH RUN</t>
+        </is>
+      </c>
+      <c r="C12" t="n">
+        <v>-1454.38</v>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>BK555827</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>2024-04-20</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>POS DEBIT FOURTH COFFEE INV-2047</t>
+        </is>
+      </c>
+      <c r="C13" t="n">
+        <v>-434.17</v>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>BK127259</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>2024-04-29</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>SERVICE CHARGE - ACCOUNT MAINTENANCE</t>
+        </is>
+      </c>
+      <c r="C14" t="n">
+        <v>-33.31</v>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>BK784962</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>2024-04-30</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>ACH DEBIT PROSEWARE LEGAL</t>
+        </is>
+      </c>
+      <c r="C15" t="n">
+        <v>-287.53</v>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>BK813394</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>2024-04-08</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>WIRE OUT WIDE WORLD IMP</t>
+        </is>
+      </c>
+      <c r="C16" t="n">
+        <v>-1243.83</v>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>BK477012</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>2024-03-17</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>POS DEBIT FOURTH COFFEE INV-2008</t>
+        </is>
+      </c>
+      <c r="C17" t="n">
+        <v>-4634.35</v>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>BK547185</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>2024-04-16</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>WIRE IN TREY RESEARCH</t>
+        </is>
+      </c>
+      <c r="C18" t="n">
+        <v>1787.58</v>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>BK616276</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>2024-03-28</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>WIRE IN BLUE YONDER AIR</t>
+        </is>
+      </c>
+      <c r="C19" t="n">
+        <v>4011.52</v>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>BK440361</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>2024-03-18</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>WIRE OUT WIDE WORLD IMP</t>
+        </is>
+      </c>
+      <c r="C20" t="n">
+        <v>-6679.81</v>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>BK182345</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>2024-04-09</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>ACH DEBIT GRAPHIC DESIGN</t>
+        </is>
+      </c>
+      <c r="C21" t="n">
+        <v>-7234.56</v>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>BK394451</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>2024-04-13</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>ACH DEBIT PROSEWARE LEGAL BATCH RUN</t>
+        </is>
+      </c>
+      <c r="C22" t="n">
+        <v>-1688.48</v>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>BK339278</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>2024-04-03</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>POS DEBIT FOURTH COFFEE INV-2085</t>
+        </is>
+      </c>
+      <c r="C23" t="n">
+        <v>-622.42</v>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>BK526061</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>2024-01-23</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>ACH DEBIT CONTOSO SUPPLIES</t>
+        </is>
+      </c>
+      <c r="C24" t="n">
+        <v>-3124.36</v>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>BK953310</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>2024-02-15</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>WIRE OUT WIDE WORLD IMP INV-2010</t>
+        </is>
+      </c>
+      <c r="C25" t="n">
+        <v>-48.55</v>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>BK847042</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>2024-01-27</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>WIRE OUT FABRIKAM LOGISTIC</t>
+        </is>
+      </c>
+      <c r="C26" t="n">
+        <v>-2237.98</v>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>BK396866</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>2024-02-07</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>POS DEBIT FOURTH COFFEE INV-2002</t>
+        </is>
+      </c>
+      <c r="C27" t="n">
+        <v>-332.71</v>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>BK350582</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>2024-02-13</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>WIRE IN TREY RESEARCH</t>
+        </is>
+      </c>
+      <c r="C28" t="n">
+        <v>4679.1</v>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>BK788721</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>2024-01-25</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>ACH CREDIT COHO VINEYARD INV-2021</t>
+        </is>
+      </c>
+      <c r="C29" t="n">
+        <v>8352.23</v>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>BK597093</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>2024-02-11</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>ACH DEBIT GRAPHIC DESIGN</t>
+        </is>
+      </c>
+      <c r="C30" t="n">
+        <v>-2454.65</v>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>BK956834</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>2024-02-10</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>WIRE OUT FABRIKAM LOGISTIC INV-2040</t>
+        </is>
+      </c>
+      <c r="C31" t="n">
+        <v>-3593.51</v>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>BK282620</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>2024-04-08</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>CARD PURCHASE TAILSPIN TRVL INV-2051</t>
+        </is>
+      </c>
+      <c r="C32" t="n">
+        <v>-5927.36</v>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>BK649675</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>2024-03-22</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>POS DEBIT FOURTH COFFEE</t>
+        </is>
+      </c>
+      <c r="C33" t="n">
+        <v>-3346.03</v>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>BK157790</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>2024-03-23</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>CARD PURCHASE TAILSPIN TRVL</t>
+        </is>
+      </c>
+      <c r="C34" t="n">
+        <v>-6458.02</v>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>BK666659</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>2024-01-13</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>WIRE IN BLUE YONDER AIR</t>
+        </is>
+      </c>
+      <c r="C35" t="n">
+        <v>6550.01</v>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>BK798825</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>2024-04-27</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>CARD PURCHASE LITWARE HOST INV-2018</t>
+        </is>
+      </c>
+      <c r="C36" t="n">
+        <v>-1946.81</v>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>BK704587</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>2024-04-10</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>ACH CREDIT COHO VINEYARD</t>
+        </is>
+      </c>
+      <c r="C37" t="n">
+        <v>3401.03</v>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>BK434551</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>2024-03-04</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>ACH DEBIT CONTOSO SUPPLIES</t>
+        </is>
+      </c>
+      <c r="C38" t="n">
+        <v>-8559.18</v>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>BK325899</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>2024-04-21</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>POS DEBIT ADATUM CLEANING</t>
+        </is>
+      </c>
+      <c r="C39" t="n">
+        <v>-1123.58</v>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>BK182628</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>2024-04-28</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>WIRE IN ALPINE RETAIL</t>
+        </is>
+      </c>
+      <c r="C40" t="n">
+        <v>4646.97</v>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>BK569048</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>2024-03-03</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>WIRE OUT FABRIKAM LOGISTIC BATCH RUN</t>
+        </is>
+      </c>
+      <c r="C41" t="n">
+        <v>-1944.39</v>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>BK950452</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>2024-04-06</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>ACH DEBIT NORTHWIND TRADERS</t>
+        </is>
+      </c>
+      <c r="C42" t="n">
+        <v>-5806.03</v>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>BK748874</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>2024-04-30</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>ACH DEBIT GRAPHIC DESIGN</t>
+        </is>
+      </c>
+      <c r="C43" t="n">
+        <v>-1344.67</v>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>BK741407</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>2024-01-14</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>SERVICE CHARGE - ACCOUNT MAINTENANCE</t>
+        </is>
+      </c>
+      <c r="C44" t="n">
+        <v>-38.16</v>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>BK784862</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>2024-04-08</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>POS DEBIT ADATUM CLEANING</t>
+        </is>
+      </c>
+      <c r="C45" t="n">
+        <v>-3424.32</v>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>BK980872</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>2024-02-01</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>WIRE OUT FABRIKAM LOGISTIC</t>
+        </is>
+      </c>
+      <c r="C46" t="n">
+        <v>-2248.4</v>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>BK268752</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>2024-04-17</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>POS DEBIT ADATUM CLEANING</t>
+        </is>
+      </c>
+      <c r="C47" t="n">
+        <v>-5779.52</v>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>BK612724</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>2024-03-03</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>WIRE IN ALPINE RETAIL</t>
+        </is>
+      </c>
+      <c r="C48" t="n">
+        <v>167.56</v>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>BK519584</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>2024-01-05</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>ACH DEBIT NORTHWIND TRADERS INV-2025</t>
+        </is>
+      </c>
+      <c r="C49" t="n">
+        <v>-3359.08</v>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>BK127315</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>2024-02-27</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>ACH DEBIT PROSEWARE LEGAL</t>
+        </is>
+      </c>
+      <c r="C50" t="n">
+        <v>-4935.5</v>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>BK389946</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>2024-01-04</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>ACH DEBIT NORTHWIND TRADERS</t>
+        </is>
+      </c>
+      <c r="C51" t="n">
+        <v>-2805.47</v>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>BK944506</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>2024-02-20</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>ACH DEBIT GRAPHIC DESIGN</t>
+        </is>
+      </c>
+      <c r="C52" t="n">
+        <v>-2166.81</v>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>BK134251</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>2024-04-23</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>CARD PURCHASE TAILSPIN TRVL</t>
+        </is>
+      </c>
+      <c r="C53" t="n">
+        <v>-7589.58</v>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>BK799403</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>2024-01-11</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>ACH DEBIT PROSEWARE LEGAL INV-2065</t>
+        </is>
+      </c>
+      <c r="C54" t="n">
+        <v>-6778.3</v>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>BK621148</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>2024-04-09</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>CARD PURCHASE LITWARE HOST</t>
+        </is>
+      </c>
+      <c r="C55" t="n">
+        <v>-369.16</v>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>BK817361</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>2024-02-23</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>ACH DEBIT NORTHWIND TRADERS</t>
+        </is>
+      </c>
+      <c r="C56" t="n">
+        <v>-7957.04</v>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>BK437836</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>2024-04-15</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>CARD PURCHASE LITWARE HOST</t>
+        </is>
+      </c>
+      <c r="C57" t="n">
+        <v>-3107.73</v>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>BK631261</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>2024-01-03</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>ACH DEBIT GRAPHIC DESIGN INV-2009</t>
+        </is>
+      </c>
+      <c r="C58" t="n">
+        <v>-1743.73</v>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>BK722828</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>2024-03-18</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>CARD PURCHASE LITWARE HOST</t>
+        </is>
+      </c>
+      <c r="C59" t="n">
+        <v>-1667.25</v>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>BK155678</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>2024-02-24</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>ACH DEBIT GRAPHIC DESIGN</t>
+        </is>
+      </c>
+      <c r="C60" t="n">
+        <v>-167.56</v>
+      </c>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>BK554092</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>2024-03-15</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>POS DEBIT FOURTH COFFEE INV-2006</t>
+        </is>
+      </c>
+      <c r="C61" t="n">
+        <v>-332.71</v>
+      </c>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>BK139547</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>2024-03-14</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>CARD PURCHASE LITWARE HOST INV-2016</t>
+        </is>
+      </c>
+      <c r="C62" t="n">
+        <v>-5747.4</v>
+      </c>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>BK708804</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>2024-04-02</t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>SERVICE CHARGE - ACCOUNT MAINTENANCE</t>
+        </is>
+      </c>
+      <c r="C63" t="n">
+        <v>-29</v>
+      </c>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>BK383815</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>2024-01-09</t>
+        </is>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>WIRE IN ALPINE RETAIL INV-2014</t>
+        </is>
+      </c>
+      <c r="C64" t="n">
+        <v>3497.87</v>
+      </c>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t>BK390732</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>2024-03-15</t>
+        </is>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>WIRE OUT FABRIKAM LOGISTIC</t>
+        </is>
+      </c>
+      <c r="C65" t="n">
+        <v>-879.77</v>
+      </c>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t>BK695071</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>2024-01-06</t>
+        </is>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>CARD PURCHASE LITWARE HOST</t>
+        </is>
+      </c>
+      <c r="C66" t="n">
+        <v>-7601.22</v>
+      </c>
+      <c r="D66" t="inlineStr">
+        <is>
+          <t>BK588132</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>2024-01-11</t>
+        </is>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>ACH DEBIT CONTOSO SUPPLIES INV-2066</t>
+        </is>
+      </c>
+      <c r="C67" t="n">
+        <v>-6872.18</v>
+      </c>
+      <c r="D67" t="inlineStr">
+        <is>
+          <t>BK217970</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>2024-04-20</t>
+        </is>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>SERVICE CHARGE - ACCOUNT MAINTENANCE</t>
+        </is>
+      </c>
+      <c r="C68" t="n">
+        <v>-40.23</v>
+      </c>
+      <c r="D68" t="inlineStr">
+        <is>
+          <t>BK518556</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>2024-03-07</t>
+        </is>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>POS DEBIT ADATUM CLEANING BATCH RUN</t>
+        </is>
+      </c>
+      <c r="C69" t="n">
+        <v>-386.93</v>
+      </c>
+      <c r="D69" t="inlineStr">
+        <is>
+          <t>BK981636</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>2024-03-29</t>
+        </is>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>ACH DEBIT NORTHWIND TRADERS</t>
+        </is>
+      </c>
+      <c r="C70" t="n">
+        <v>-2049.41</v>
+      </c>
+      <c r="D70" t="inlineStr">
+        <is>
+          <t>BK278668</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>2024-02-07</t>
+        </is>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>POS DEBIT ADATUM CLEANING</t>
+        </is>
+      </c>
+      <c r="C71" t="n">
+        <v>-8652.74</v>
+      </c>
+      <c r="D71" t="inlineStr">
+        <is>
+          <t>BK519255</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>2024-03-18</t>
+        </is>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>POS DEBIT ADATUM CLEANING</t>
+        </is>
+      </c>
+      <c r="C72" t="n">
+        <v>-1672.24</v>
+      </c>
+      <c r="D72" t="inlineStr">
+        <is>
+          <t>BK783544</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>2024-02-16</t>
+        </is>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>POS DEBIT FOURTH COFFEE</t>
+        </is>
+      </c>
+      <c r="C73" t="n">
+        <v>-2286.18</v>
+      </c>
+      <c r="D73" t="inlineStr">
+        <is>
+          <t>BK510858</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>2024-04-01</t>
+        </is>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>WIRE IN TREY RESEARCH INV-2084</t>
+        </is>
+      </c>
+      <c r="C74" t="n">
+        <v>1727.16</v>
+      </c>
+      <c r="D74" t="inlineStr">
+        <is>
+          <t>BK922984</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>2024-03-07</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>SERVICE CHARGE - ACCOUNT MAINTENANCE</t>
+        </is>
+      </c>
+      <c r="C75" t="n">
+        <v>-6.62</v>
+      </c>
+      <c r="D75" t="inlineStr">
+        <is>
+          <t>BK923459</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>2024-01-17</t>
+        </is>
+      </c>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>POS DEBIT FOURTH COFFEE INV-2067</t>
+        </is>
+      </c>
+      <c r="C76" t="n">
+        <v>-745.14</v>
+      </c>
+      <c r="D76" t="inlineStr">
+        <is>
+          <t>BK915752</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>2024-04-15</t>
+        </is>
+      </c>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>POS DEBIT ADATUM CLEANING INV-2059</t>
+        </is>
+      </c>
+      <c r="C77" t="n">
+        <v>-8038.14</v>
+      </c>
+      <c r="D77" t="inlineStr">
+        <is>
+          <t>BK245360</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>2024-01-16</t>
+        </is>
+      </c>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>ACH DEBIT CONTOSO SUPPLIES</t>
+        </is>
+      </c>
+      <c r="C78" t="n">
+        <v>-1603.62</v>
+      </c>
+      <c r="D78" t="inlineStr">
+        <is>
+          <t>BK617457</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>2024-04-02</t>
+        </is>
+      </c>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>ACH DEBIT NORTHWIND TRADERS INV-2045</t>
+        </is>
+      </c>
+      <c r="C79" t="n">
+        <v>-7339.77</v>
+      </c>
+      <c r="D79" t="inlineStr">
+        <is>
+          <t>BK756989</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>2024-03-31</t>
+        </is>
+      </c>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>WIRE OUT WIDE WORLD IMP</t>
+        </is>
+      </c>
+      <c r="C80" t="n">
+        <v>-5232.17</v>
+      </c>
+      <c r="D80" t="inlineStr">
+        <is>
+          <t>BK483984</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>2024-03-07</t>
+        </is>
+      </c>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>ACH DEBIT GRAPHIC DESIGN</t>
+        </is>
+      </c>
+      <c r="C81" t="n">
+        <v>-6498.94</v>
+      </c>
+      <c r="D81" t="inlineStr">
+        <is>
+          <t>BK443314</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="inlineStr">
+        <is>
+          <t>2024-01-31</t>
+        </is>
+      </c>
+      <c r="B82" t="inlineStr">
+        <is>
+          <t>CARD PURCHASE TAILSPIN TRVL INV-2088</t>
+        </is>
+      </c>
+      <c r="C82" t="n">
+        <v>-3556.08</v>
+      </c>
+      <c r="D82" t="inlineStr">
+        <is>
+          <t>BK304461</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="inlineStr">
+        <is>
+          <t>2024-03-20</t>
+        </is>
+      </c>
+      <c r="B83" t="inlineStr">
+        <is>
+          <t>CARD PURCHASE LITWARE HOST</t>
+        </is>
+      </c>
+      <c r="C83" t="n">
+        <v>-1943.87</v>
+      </c>
+      <c r="D83" t="inlineStr">
+        <is>
+          <t>BK607338</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="inlineStr">
+        <is>
+          <t>2024-03-14</t>
+        </is>
+      </c>
+      <c r="B84" t="inlineStr">
+        <is>
+          <t>ACH CREDIT COHO VINEYARD</t>
+        </is>
+      </c>
+      <c r="C84" t="n">
+        <v>4320.58</v>
+      </c>
+      <c r="D84" t="inlineStr">
+        <is>
+          <t>BK635215</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="inlineStr">
+        <is>
+          <t>2024-01-14</t>
+        </is>
+      </c>
+      <c r="B85" t="inlineStr">
+        <is>
+          <t>ACH DEBIT PROSEWARE LEGAL</t>
+        </is>
+      </c>
+      <c r="C85" t="n">
+        <v>-3434.55</v>
+      </c>
+      <c r="D85" t="inlineStr">
+        <is>
+          <t>BK220348</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="inlineStr">
+        <is>
+          <t>2024-04-29</t>
+        </is>
+      </c>
+      <c r="B86" t="inlineStr">
+        <is>
+          <t>SERVICE CHARGE - ACCOUNT MAINTENANCE</t>
+        </is>
+      </c>
+      <c r="C86" t="n">
+        <v>-14.46</v>
+      </c>
+      <c r="D86" t="inlineStr">
+        <is>
+          <t>BK159758</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="inlineStr">
+        <is>
+          <t>2024-02-23</t>
+        </is>
+      </c>
+      <c r="B87" t="inlineStr">
+        <is>
+          <t>ACH DEBIT PROSEWARE LEGAL INV-2017</t>
+        </is>
+      </c>
+      <c r="C87" t="n">
+        <v>-2167.48</v>
+      </c>
+      <c r="D87" t="inlineStr">
+        <is>
+          <t>BK462248</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="inlineStr">
+        <is>
+          <t>2024-01-06</t>
+        </is>
+      </c>
+      <c r="B88" t="inlineStr">
+        <is>
+          <t>WIRE IN ALPINE RETAIL</t>
+        </is>
+      </c>
+      <c r="C88" t="n">
+        <v>5319.63</v>
+      </c>
+      <c r="D88" t="inlineStr">
+        <is>
+          <t>BK249409</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="inlineStr">
+        <is>
+          <t>2024-01-27</t>
+        </is>
+      </c>
+      <c r="B89" t="inlineStr">
+        <is>
+          <t>CARD PURCHASE LITWARE HOST INV-2041</t>
+        </is>
+      </c>
+      <c r="C89" t="n">
+        <v>-8240.450000000001</v>
+      </c>
+      <c r="D89" t="inlineStr">
+        <is>
+          <t>BK856151</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="inlineStr">
+        <is>
+          <t>2024-04-21</t>
+        </is>
+      </c>
+      <c r="B90" t="inlineStr">
+        <is>
+          <t>WIRE OUT FABRIKAM LOGISTIC</t>
+        </is>
+      </c>
+      <c r="C90" t="n">
+        <v>-3496.08</v>
+      </c>
+      <c r="D90" t="inlineStr">
+        <is>
+          <t>BK224034</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="inlineStr">
+        <is>
+          <t>2024-02-07</t>
+        </is>
+      </c>
+      <c r="B91" t="inlineStr">
+        <is>
+          <t>WIRE IN ALPINE RETAIL INV-2000</t>
+        </is>
+      </c>
+      <c r="C91" t="n">
+        <v>287.53</v>
+      </c>
+      <c r="D91" t="inlineStr">
+        <is>
+          <t>BK886197</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="inlineStr">
+        <is>
+          <t>2024-04-27</t>
+        </is>
+      </c>
+      <c r="B92" t="inlineStr">
+        <is>
+          <t>CARD PURCHASE LITWARE HOST</t>
+        </is>
+      </c>
+      <c r="C92" t="n">
+        <v>-5924.98</v>
+      </c>
+      <c r="D92" t="inlineStr">
+        <is>
+          <t>BK485397</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="inlineStr">
+        <is>
+          <t>2024-04-29</t>
+        </is>
+      </c>
+      <c r="B93" t="inlineStr">
+        <is>
+          <t>POS DEBIT ADATUM CLEANING INV-2005</t>
+        </is>
+      </c>
+      <c r="C93" t="n">
+        <v>-369.16</v>
+      </c>
+      <c r="D93" t="inlineStr">
+        <is>
+          <t>BK293777</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="inlineStr">
+        <is>
+          <t>2024-04-13</t>
+        </is>
+      </c>
+      <c r="B94" t="inlineStr">
+        <is>
+          <t>ACH DEBIT GRAPHIC DESIGN INV-2053</t>
+        </is>
+      </c>
+      <c r="C94" t="n">
+        <v>-470.63</v>
+      </c>
+      <c r="D94" t="inlineStr">
+        <is>
+          <t>BK404793</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="inlineStr">
+        <is>
+          <t>2024-04-20</t>
+        </is>
+      </c>
+      <c r="B95" t="inlineStr">
+        <is>
+          <t>ACH DEBIT GRAPHIC DESIGN</t>
+        </is>
+      </c>
+      <c r="C95" t="n">
+        <v>-7221.3</v>
+      </c>
+      <c r="D95" t="inlineStr">
+        <is>
+          <t>BK889921</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="inlineStr">
+        <is>
+          <t>2024-04-24</t>
+        </is>
+      </c>
+      <c r="B96" t="inlineStr">
+        <is>
+          <t>CARD PURCHASE LITWARE HOST INV-2020</t>
+        </is>
+      </c>
+      <c r="C96" t="n">
+        <v>-8136.69</v>
+      </c>
+      <c r="D96" t="inlineStr">
+        <is>
+          <t>BK612746</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="inlineStr">
+        <is>
+          <t>2024-01-20</t>
+        </is>
+      </c>
+      <c r="B97" t="inlineStr">
+        <is>
+          <t>ACH DEBIT GRAPHIC DESIGN</t>
+        </is>
+      </c>
+      <c r="C97" t="n">
+        <v>-8401.77</v>
+      </c>
+      <c r="D97" t="inlineStr">
+        <is>
+          <t>BK104660</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="inlineStr">
+        <is>
+          <t>2024-03-02</t>
+        </is>
+      </c>
+      <c r="B98" t="inlineStr">
+        <is>
+          <t>WIRE OUT WIDE WORLD IMP</t>
+        </is>
+      </c>
+      <c r="C98" t="n">
+        <v>-7843.98</v>
+      </c>
+      <c r="D98" t="inlineStr">
+        <is>
+          <t>BK425137</t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="inlineStr">
+        <is>
+          <t>2024-02-03</t>
+        </is>
+      </c>
+      <c r="B99" t="inlineStr">
+        <is>
+          <t>ACH DEBIT PROSEWARE LEGAL</t>
+        </is>
+      </c>
+      <c r="C99" t="n">
+        <v>-7924.78</v>
+      </c>
+      <c r="D99" t="inlineStr">
+        <is>
+          <t>BK558811</t>
+        </is>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="inlineStr">
+        <is>
+          <t>2024-02-07</t>
+        </is>
+      </c>
+      <c r="B100" t="inlineStr">
+        <is>
+          <t>POS DEBIT FOURTH COFFEE INV-2068</t>
+        </is>
+      </c>
+      <c r="C100" t="n">
+        <v>-7497.66</v>
+      </c>
+      <c r="D100" t="inlineStr">
+        <is>
+          <t>BK657930</t>
+        </is>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="inlineStr">
+        <is>
+          <t>2024-01-08</t>
+        </is>
+      </c>
+      <c r="B101" t="inlineStr">
+        <is>
+          <t>WIRE OUT WIDE WORLD IMP</t>
+        </is>
+      </c>
+      <c r="C101" t="n">
+        <v>-8958.32</v>
+      </c>
+      <c r="D101" t="inlineStr">
+        <is>
+          <t>BK899828</t>
+        </is>
       </c>
     </row>
   </sheetData>
@@ -506,293 +2450,2149 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C5"/>
+  <dimension ref="A1:D107"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>Date</t>
+          <t>Entry Date</t>
         </is>
       </c>
       <c r="B1" t="inlineStr">
         <is>
-          <t>Description</t>
+          <t>Memo</t>
         </is>
       </c>
       <c r="C1" t="inlineStr">
         <is>
-          <t>Amount</t>
+          <t>Document No</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>Net Amount</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2023-10-01</t>
+          <t>15/04/2024</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Payment to Vendor A</t>
-        </is>
-      </c>
-      <c r="C2" t="n">
-        <v>-1500</v>
+          <t>Litware cloud hosting Litware Hosting</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>INV-2019</t>
+        </is>
+      </c>
+      <c r="D2" t="n">
+        <v>-5965</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2023-10-03</t>
+          <t>08/03/2024</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Coffee</t>
-        </is>
-      </c>
-      <c r="C3" t="n">
-        <v>-4.5</v>
+          <t>Wide World Importers goods Wide World Importers</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>INV-2052</t>
+        </is>
+      </c>
+      <c r="D3" t="n">
+        <v>-371.58</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2023-10-05</t>
+          <t>09/02/2024</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Invoice 102 - Client B</t>
-        </is>
-      </c>
-      <c r="C4" t="n">
-        <v>5000</v>
+          <t>Adatum office cleaning Adatum Cleaning</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>INV-2043</t>
+        </is>
+      </c>
+      <c r="D4" t="n">
+        <v>-8652.74</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2023-10-09</t>
+          <t>18/04/2024</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Bank Fee</t>
-        </is>
-      </c>
-      <c r="C5" t="n">
-        <v>-15</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:I5"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1">
-      <c r="A1" t="inlineStr">
-        <is>
-          <t>Date</t>
-        </is>
-      </c>
-      <c r="B1" t="inlineStr">
-        <is>
-          <t>Description</t>
-        </is>
-      </c>
-      <c r="C1" t="inlineStr">
-        <is>
-          <t>Amount</t>
-        </is>
-      </c>
-      <c r="D1" t="inlineStr">
-        <is>
-          <t>Matched_Row_Index_in_Sheet2</t>
-        </is>
-      </c>
-      <c r="E1" t="inlineStr">
-        <is>
-          <t>Match_Distance</t>
-        </is>
-      </c>
-      <c r="F1" t="inlineStr">
-        <is>
-          <t>Match_Confidence</t>
-        </is>
-      </c>
-      <c r="G1" t="inlineStr">
-        <is>
-          <t>Matched_Date</t>
-        </is>
-      </c>
-      <c r="H1" t="inlineStr">
-        <is>
-          <t>Matched_Description</t>
-        </is>
-      </c>
-      <c r="I1" t="inlineStr">
-        <is>
-          <t>Matched_Amount</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>2023-10-01</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>ACH Transfer - Vendor A</t>
-        </is>
-      </c>
-      <c r="C2" t="n">
-        <v>-1500</v>
-      </c>
-      <c r="D2" t="n">
-        <v>0</v>
-      </c>
-      <c r="E2" t="n">
-        <v>0.4117326600440865</v>
-      </c>
-      <c r="F2" t="n">
-        <v>0.5882673399559135</v>
-      </c>
-      <c r="G2" t="inlineStr">
-        <is>
-          <t>2023-10-01</t>
-        </is>
-      </c>
-      <c r="H2" t="inlineStr">
-        <is>
-          <t>Payment to Vendor A</t>
-        </is>
-      </c>
-      <c r="I2" t="n">
-        <v>-1500</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>2023-10-02</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>POS Debit - Coffee Shop</t>
-        </is>
-      </c>
-      <c r="C3" t="n">
-        <v>-4.5</v>
-      </c>
-      <c r="D3" t="n">
-        <v>1</v>
-      </c>
-      <c r="E3" t="n">
-        <v>0.4713576414634609</v>
-      </c>
-      <c r="F3" t="n">
-        <v>0.5286423585365391</v>
-      </c>
-      <c r="G3" t="inlineStr">
-        <is>
-          <t>2023-10-03</t>
-        </is>
-      </c>
-      <c r="H3" t="inlineStr">
-        <is>
-          <t>Coffee</t>
-        </is>
-      </c>
-      <c r="I3" t="n">
-        <v>-4.5</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>2023-10-05</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>Wire Transfer IN - Client B</t>
-        </is>
-      </c>
-      <c r="C4" t="n">
-        <v>5000</v>
-      </c>
-      <c r="D4" t="n">
-        <v>2</v>
-      </c>
-      <c r="E4" t="n">
-        <v>0.4420271824503862</v>
-      </c>
-      <c r="F4" t="n">
-        <v>0.5579728175496138</v>
-      </c>
-      <c r="G4" t="inlineStr">
-        <is>
-          <t>2023-10-05</t>
-        </is>
-      </c>
-      <c r="H4" t="inlineStr">
-        <is>
-          <t>Invoice 102 - Client B</t>
-        </is>
-      </c>
-      <c r="I4" t="n">
-        <v>5000</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>2023-10-10</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>Fee - Monthly Maintenance</t>
-        </is>
-      </c>
-      <c r="C5" t="n">
-        <v>-15</v>
+          <t>Fourth Coffee pantry Fourth Coffee</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>INV-2047</t>
+        </is>
       </c>
       <c r="D5" t="n">
-        <v>3</v>
-      </c>
-      <c r="E5" t="n">
-        <v>0.6683606358146037</v>
-      </c>
-      <c r="F5" t="n">
-        <v>0.3316393641853963</v>
-      </c>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t>2023-10-09</t>
-        </is>
-      </c>
-      <c r="H5" t="inlineStr">
-        <is>
-          <t>Bank Fee</t>
-        </is>
-      </c>
-      <c r="I5" t="n">
-        <v>-15</v>
+        <v>-434.17</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>17/04/2024</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Trey Research settlement Trey Research</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>INV-2056</t>
+        </is>
+      </c>
+      <c r="D6" t="n">
+        <v>1787.58</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>30/03/2024</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Fabrikam Logistics freight Fabrikam Logistics</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>INV-5030</t>
+        </is>
+      </c>
+      <c r="D7" t="n">
+        <v>-1165.39</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>25/01/2024</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Fabrikam Logistics freight Fabrikam Logistics</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>INV-2064</t>
+        </is>
+      </c>
+      <c r="D8" t="n">
+        <v>-2237.98</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>14/03/2024</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Litware cloud hosting Litware Hosting</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>INV-2016</t>
+        </is>
+      </c>
+      <c r="D9" t="n">
+        <v>-5747.4</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>14/01/2024</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Contoso Supplies invoice Contoso Supplies</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>INV-2066</t>
+        </is>
+      </c>
+      <c r="D10" t="n">
+        <v>-6872.18</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>29/04/2024</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Litware cloud hosting Litware Hosting</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>INV-2026</t>
+        </is>
+      </c>
+      <c r="D11" t="n">
+        <v>-5924.98</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>21/02/2024</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Graphic Design Institute Graphic Design Inst</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>INV-2023</t>
+        </is>
+      </c>
+      <c r="D12" t="n">
+        <v>-2166.81</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>14/04/2024</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>Proseware legal fees Proseware Legal</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>INV-5002</t>
+        </is>
+      </c>
+      <c r="D13" t="n">
+        <v>-820.34</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>19/02/2024</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>Fourth Coffee pantry Fourth Coffee</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>INV-2061</t>
+        </is>
+      </c>
+      <c r="D14" t="n">
+        <v>-2286.18</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>12/03/2024</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>Coho Vineyard payment received Coho Vineyard</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>INV-2042</t>
+        </is>
+      </c>
+      <c r="D15" t="n">
+        <v>4320.58</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>07/02/2024</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>Fourth Coffee pantry Fourth Coffee</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>INV-2068</t>
+        </is>
+      </c>
+      <c r="D16" t="n">
+        <v>-7497.66</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>26/02/2024</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>Payment - Northwind Traders Ltd Northwind Traders</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>INV-2069</t>
+        </is>
+      </c>
+      <c r="D17" t="n">
+        <v>-7957.04</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>01/03/2024</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>Fabrikam Logistics freight Fabrikam Logistics</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>INV-5011</t>
+        </is>
+      </c>
+      <c r="D18" t="n">
+        <v>-666.64</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>12/03/2024</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>Fourth Coffee pantry Fourth Coffee</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>INV-2006</t>
+        </is>
+      </c>
+      <c r="D19" t="n">
+        <v>-332.71</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>29/01/2024</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>Litware cloud hosting Litware Hosting</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>INV-2041</t>
+        </is>
+      </c>
+      <c r="D20" t="n">
+        <v>-8240.450000000001</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>01/04/2024</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>Fourth Coffee pantry Fourth Coffee</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>INV-2085</t>
+        </is>
+      </c>
+      <c r="D21" t="n">
+        <v>-622.42</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>23/04/2024</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>Fabrikam Logistics freight Fabrikam Logistics</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>INV-2080</t>
+        </is>
+      </c>
+      <c r="D22" t="n">
+        <v>-3496.08</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>01/05/2024</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>Invoice settled - Alpine Retail Alpine Retail</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>INV-2035</t>
+        </is>
+      </c>
+      <c r="D23" t="n">
+        <v>4646.97</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>13/04/2024</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>Proseware legal fees Proseware Legal</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>INV-5001</t>
+        </is>
+      </c>
+      <c r="D24" t="n">
+        <v>-261.26</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>03/03/2024</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>Wide World Importers goods Wide World Importers</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>INV-2013</t>
+        </is>
+      </c>
+      <c r="D25" t="n">
+        <v>-7843.98</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>12/04/2024</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>Litware cloud hosting Litware Hosting</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>INV-2027</t>
+        </is>
+      </c>
+      <c r="D26" t="n">
+        <v>-3107.73</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>20/03/2024</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>Litware cloud hosting Litware Hosting</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>INV-2044</t>
+        </is>
+      </c>
+      <c r="D27" t="n">
+        <v>-1667.25</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>06/03/2024</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>Contoso Supplies invoice Contoso Supplies</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>INV-2038</t>
+        </is>
+      </c>
+      <c r="D28" t="n">
+        <v>-8559.18</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>24/02/2024</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>Graphic Design Institute Graphic Design Inst</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>INV-2003</t>
+        </is>
+      </c>
+      <c r="D29" t="n">
+        <v>-167.56</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>19/01/2024</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>Fourth Coffee pantry Fourth Coffee</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>INV-2067</t>
+        </is>
+      </c>
+      <c r="D30" t="n">
+        <v>-745.14</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>06/04/2024</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>Tailspin travel booking Tailspin Travel</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>INV-2051</t>
+        </is>
+      </c>
+      <c r="D31" t="n">
+        <v>-5927.36</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>13/04/2024</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>Tailspin travel booking Tailspin Travel</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>INV-2055</t>
+        </is>
+      </c>
+      <c r="D32" t="n">
+        <v>-7177.19</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>09/04/2024</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>Adatum office cleaning Adatum Cleaning</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>INV-2015</t>
+        </is>
+      </c>
+      <c r="D33" t="n">
+        <v>-3424.32</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>22/01/2024</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>Contoso Supplies invoice Contoso Supplies</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>INV-2033</t>
+        </is>
+      </c>
+      <c r="D34" t="n">
+        <v>-3124.36</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>09/03/2024</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>Adatum office cleaning Adatum Cleaning</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>INV-5021</t>
+        </is>
+      </c>
+      <c r="D35" t="n">
+        <v>-180.17</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>06/01/2024</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>Litware cloud hosting Litware Hosting</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>INV-2078</t>
+        </is>
+      </c>
+      <c r="D36" t="n">
+        <v>-7601.22</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>10/04/2024</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>Wide World Importers goods Wide World Importers</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>INV-2030</t>
+        </is>
+      </c>
+      <c r="D37" t="n">
+        <v>-1243.83</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>15/03/2024</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>Fabrikam Logistics freight Fabrikam Logistics</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>INV-2057</t>
+        </is>
+      </c>
+      <c r="D38" t="n">
+        <v>-879.77</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>03/04/2024</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>Payment - Northwind Traders Ltd Northwind Traders</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>INV-2074</t>
+        </is>
+      </c>
+      <c r="D39" t="n">
+        <v>-5806.03</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>18/03/2024</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>Litware cloud hosting Litware Hosting</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>INV-2060</t>
+        </is>
+      </c>
+      <c r="D40" t="n">
+        <v>-1943.87</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>19/01/2024</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>Graphic Design Institute Graphic Design Inst</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>INV-2029</t>
+        </is>
+      </c>
+      <c r="D41" t="n">
+        <v>-8401.77</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>10/01/2024</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>Invoice settled - Alpine Retail Alpine Retail</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>INV-2014</t>
+        </is>
+      </c>
+      <c r="D42" t="n">
+        <v>3497.87</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>20/02/2024</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>Proseware legal fees Proseware Legal</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>INV-2017</t>
+        </is>
+      </c>
+      <c r="D43" t="n">
+        <v>-2167.48</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>26/03/2024</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>Blue Yonder Airlines receipt Blue Yonder Airlines</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>INV-2077</t>
+        </is>
+      </c>
+      <c r="D44" t="n">
+        <v>4011.52</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>16/02/2024</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>Wide World Importers goods Wide World Importers</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>INV-2010</t>
+        </is>
+      </c>
+      <c r="D45" t="n">
+        <v>-48.55</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>09/03/2024</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>Graphic Design Institute Graphic Design Inst</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>INV-2079</t>
+        </is>
+      </c>
+      <c r="D46" t="n">
+        <v>-6498.94</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>29/04/2024</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>Adatum office cleaning Adatum Cleaning</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>INV-2005</t>
+        </is>
+      </c>
+      <c r="D47" t="n">
+        <v>-369.16</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>06/03/2024</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>Invoice settled - Alpine Retail Alpine Retail</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>INV-2007</t>
+        </is>
+      </c>
+      <c r="D48" t="n">
+        <v>167.56</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>17/02/2024</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>Adatum office cleaning Adatum Cleaning</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>INV-2037</t>
+        </is>
+      </c>
+      <c r="D49" t="n">
+        <v>-8305.99</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>05/04/2024</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>Payment - Northwind Traders Ltd Northwind Traders</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>INV-2045</t>
+        </is>
+      </c>
+      <c r="D50" t="n">
+        <v>-7339.77</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>05/04/2024</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>Accrual - goods received not invoiced</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>ACC-9004</t>
+        </is>
+      </c>
+      <c r="D51" t="n">
+        <v>-2305.08</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>30/03/2024</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>Fabrikam Logistics freight Fabrikam Logistics</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>INV-5031</t>
+        </is>
+      </c>
+      <c r="D52" t="n">
+        <v>-288.99</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>09/04/2024</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>Coho Vineyard payment received Coho Vineyard</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>INV-2063</t>
+        </is>
+      </c>
+      <c r="D53" t="n">
+        <v>3401.03</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>30/03/2024</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>Graphic Design Institute Graphic Design Inst</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>INV-2072</t>
+        </is>
+      </c>
+      <c r="D54" t="n">
+        <v>-1729.68</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>03/01/2024</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>Graphic Design Institute Graphic Design Inst</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>INV-2031</t>
+        </is>
+      </c>
+      <c r="D55" t="n">
+        <v>-5661.73</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>05/02/2024</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>Invoice settled - Alpine Retail Alpine Retail</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>INV-2000</t>
+        </is>
+      </c>
+      <c r="D56" t="n">
+        <v>287.53</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>04/03/2024</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>Fabrikam Logistics freight Fabrikam Logistics</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>INV-5010</t>
+        </is>
+      </c>
+      <c r="D57" t="n">
+        <v>-772.8099999999999</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>20/04/2024</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>Tailspin travel booking Tailspin Travel</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>INV-2075</t>
+        </is>
+      </c>
+      <c r="D58" t="n">
+        <v>-7589.58</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>13/01/2024</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>Proseware legal fees Proseware Legal</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>INV-2065</t>
+        </is>
+      </c>
+      <c r="D59" t="n">
+        <v>-6778.3</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>21/01/2024</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>Accrual - goods received not invoiced</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>ACC-9005</t>
+        </is>
+      </c>
+      <c r="D60" t="n">
+        <v>-1523.88</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>12/04/2024</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>Adatum office cleaning Adatum Cleaning</t>
+        </is>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>INV-2059</t>
+        </is>
+      </c>
+      <c r="D61" t="n">
+        <v>-8038.14</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>06/02/2024</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>Accrual - goods received not invoiced</t>
+        </is>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>ACC-9000</t>
+        </is>
+      </c>
+      <c r="D62" t="n">
+        <v>-1729.17</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>31/03/2024</t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>Fabrikam Logistics freight Fabrikam Logistics</t>
+        </is>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>INV-2073</t>
+        </is>
+      </c>
+      <c r="D63" t="n">
+        <v>-8070.83</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>12/02/2024</t>
+        </is>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>Fabrikam Logistics freight Fabrikam Logistics</t>
+        </is>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>INV-2040</t>
+        </is>
+      </c>
+      <c r="D64" t="n">
+        <v>-3593.51</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>06/02/2024</t>
+        </is>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>Fourth Coffee pantry Fourth Coffee</t>
+        </is>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>INV-2002</t>
+        </is>
+      </c>
+      <c r="D65" t="n">
+        <v>-332.71</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>15/03/2024</t>
+        </is>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>Fourth Coffee pantry Fourth Coffee</t>
+        </is>
+      </c>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>INV-2008</t>
+        </is>
+      </c>
+      <c r="D66" t="n">
+        <v>-4634.35</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>27/02/2024</t>
+        </is>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>Proseware legal fees Proseware Legal</t>
+        </is>
+      </c>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>INV-2024</t>
+        </is>
+      </c>
+      <c r="D67" t="n">
+        <v>-4935.5</v>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>16/01/2024</t>
+        </is>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>Proseware legal fees Proseware Legal</t>
+        </is>
+      </c>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>INV-2062</t>
+        </is>
+      </c>
+      <c r="D68" t="n">
+        <v>-3434.55</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>24/04/2024</t>
+        </is>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>Litware cloud hosting Litware Hosting</t>
+        </is>
+      </c>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>INV-2018</t>
+        </is>
+      </c>
+      <c r="D69" t="n">
+        <v>-1946.81</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>13/02/2024</t>
+        </is>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>Trey Research settlement Trey Research</t>
+        </is>
+      </c>
+      <c r="C70" t="inlineStr">
+        <is>
+          <t>INV-2028</t>
+        </is>
+      </c>
+      <c r="D70" t="n">
+        <v>4679.1</v>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>04/01/2024</t>
+        </is>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>Payment - Northwind Traders Ltd Northwind Traders</t>
+        </is>
+      </c>
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>INV-2050</t>
+        </is>
+      </c>
+      <c r="D71" t="n">
+        <v>-2805.47</v>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>20/03/2024</t>
+        </is>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>Tailspin travel booking Tailspin Travel</t>
+        </is>
+      </c>
+      <c r="C72" t="inlineStr">
+        <is>
+          <t>INV-2039</t>
+        </is>
+      </c>
+      <c r="D72" t="n">
+        <v>-6458.02</v>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>12/01/2024</t>
+        </is>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>Contoso Supplies invoice Contoso Supplies</t>
+        </is>
+      </c>
+      <c r="C73" t="inlineStr">
+        <is>
+          <t>INV-2054</t>
+        </is>
+      </c>
+      <c r="D73" t="n">
+        <v>-5645.11</v>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>01/02/2024</t>
+        </is>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>Proseware legal fees Proseware Legal</t>
+        </is>
+      </c>
+      <c r="C74" t="inlineStr">
+        <is>
+          <t>INV-2011</t>
+        </is>
+      </c>
+      <c r="D74" t="n">
+        <v>-7924.78</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>10/01/2024</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>Blue Yonder Airlines receipt Blue Yonder Airlines</t>
+        </is>
+      </c>
+      <c r="C75" t="inlineStr">
+        <is>
+          <t>INV-2070</t>
+        </is>
+      </c>
+      <c r="D75" t="n">
+        <v>6550.01</v>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>16/01/2024</t>
+        </is>
+      </c>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>Contoso Supplies invoice Contoso Supplies</t>
+        </is>
+      </c>
+      <c r="C76" t="inlineStr">
+        <is>
+          <t>INV-2083</t>
+        </is>
+      </c>
+      <c r="D76" t="n">
+        <v>-1603.62</v>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>09/03/2024</t>
+        </is>
+      </c>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>Adatum office cleaning Adatum Cleaning</t>
+        </is>
+      </c>
+      <c r="C77" t="inlineStr">
+        <is>
+          <t>INV-5020</t>
+        </is>
+      </c>
+      <c r="D77" t="n">
+        <v>-206.76</v>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>27/04/2024</t>
+        </is>
+      </c>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>Litware cloud hosting Litware Hosting</t>
+        </is>
+      </c>
+      <c r="C78" t="inlineStr">
+        <is>
+          <t>INV-2020</t>
+        </is>
+      </c>
+      <c r="D78" t="n">
+        <v>-8136.69</v>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>07/02/2024</t>
+        </is>
+      </c>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>Accrual - goods received not invoiced</t>
+        </is>
+      </c>
+      <c r="C79" t="inlineStr">
+        <is>
+          <t>ACC-9003</t>
+        </is>
+      </c>
+      <c r="D79" t="n">
+        <v>-1910.79</v>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>06/01/2024</t>
+        </is>
+      </c>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>Graphic Design Institute Graphic Design Inst</t>
+        </is>
+      </c>
+      <c r="C80" t="inlineStr">
+        <is>
+          <t>INV-2009</t>
+        </is>
+      </c>
+      <c r="D80" t="n">
+        <v>-1743.73</v>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>03/01/2024</t>
+        </is>
+      </c>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>Invoice settled - Alpine Retail Alpine Retail</t>
+        </is>
+      </c>
+      <c r="C81" t="inlineStr">
+        <is>
+          <t>INV-2049</t>
+        </is>
+      </c>
+      <c r="D81" t="n">
+        <v>5319.63</v>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="inlineStr">
+        <is>
+          <t>02/04/2024</t>
+        </is>
+      </c>
+      <c r="B82" t="inlineStr">
+        <is>
+          <t>Wide World Importers goods Wide World Importers</t>
+        </is>
+      </c>
+      <c r="C82" t="inlineStr">
+        <is>
+          <t>INV-2036</t>
+        </is>
+      </c>
+      <c r="D82" t="n">
+        <v>-5232.17</v>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="inlineStr">
+        <is>
+          <t>04/02/2024</t>
+        </is>
+      </c>
+      <c r="B83" t="inlineStr">
+        <is>
+          <t>Fabrikam Logistics freight Fabrikam Logistics</t>
+        </is>
+      </c>
+      <c r="C83" t="inlineStr">
+        <is>
+          <t>INV-2048</t>
+        </is>
+      </c>
+      <c r="D83" t="n">
+        <v>-2248.4</v>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="inlineStr">
+        <is>
+          <t>01/04/2024</t>
+        </is>
+      </c>
+      <c r="B84" t="inlineStr">
+        <is>
+          <t>Trey Research settlement Trey Research</t>
+        </is>
+      </c>
+      <c r="C84" t="inlineStr">
+        <is>
+          <t>INV-2084</t>
+        </is>
+      </c>
+      <c r="D84" t="n">
+        <v>1727.16</v>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="inlineStr">
+        <is>
+          <t>29/04/2024</t>
+        </is>
+      </c>
+      <c r="B85" t="inlineStr">
+        <is>
+          <t>Graphic Design Institute Graphic Design Inst</t>
+        </is>
+      </c>
+      <c r="C85" t="inlineStr">
+        <is>
+          <t>INV-2081</t>
+        </is>
+      </c>
+      <c r="D85" t="n">
+        <v>-1344.67</v>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="inlineStr">
+        <is>
+          <t>08/02/2024</t>
+        </is>
+      </c>
+      <c r="B86" t="inlineStr">
+        <is>
+          <t>Graphic Design Institute Graphic Design Inst</t>
+        </is>
+      </c>
+      <c r="C86" t="inlineStr">
+        <is>
+          <t>INV-2034</t>
+        </is>
+      </c>
+      <c r="D86" t="n">
+        <v>-2454.65</v>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="inlineStr">
+        <is>
+          <t>07/01/2024</t>
+        </is>
+      </c>
+      <c r="B87" t="inlineStr">
+        <is>
+          <t>Payment - Northwind Traders Ltd Northwind Traders</t>
+        </is>
+      </c>
+      <c r="C87" t="inlineStr">
+        <is>
+          <t>INV-2025</t>
+        </is>
+      </c>
+      <c r="D87" t="n">
+        <v>-3359.08</v>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="inlineStr">
+        <is>
+          <t>05/03/2024</t>
+        </is>
+      </c>
+      <c r="B88" t="inlineStr">
+        <is>
+          <t>Fabrikam Logistics freight Fabrikam Logistics</t>
+        </is>
+      </c>
+      <c r="C88" t="inlineStr">
+        <is>
+          <t>INV-5012</t>
+        </is>
+      </c>
+      <c r="D88" t="n">
+        <v>-504.94</v>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="inlineStr">
+        <is>
+          <t>21/03/2024</t>
+        </is>
+      </c>
+      <c r="B89" t="inlineStr">
+        <is>
+          <t>Adatum office cleaning Adatum Cleaning</t>
+        </is>
+      </c>
+      <c r="C89" t="inlineStr">
+        <is>
+          <t>INV-2076</t>
+        </is>
+      </c>
+      <c r="D89" t="n">
+        <v>-1672.24</v>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="inlineStr">
+        <is>
+          <t>21/04/2024</t>
+        </is>
+      </c>
+      <c r="B90" t="inlineStr">
+        <is>
+          <t>Adatum office cleaning Adatum Cleaning</t>
+        </is>
+      </c>
+      <c r="C90" t="inlineStr">
+        <is>
+          <t>INV-2082</t>
+        </is>
+      </c>
+      <c r="D90" t="n">
+        <v>-1123.58</v>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="inlineStr">
+        <is>
+          <t>18/03/2024</t>
+        </is>
+      </c>
+      <c r="B91" t="inlineStr">
+        <is>
+          <t>Wide World Importers goods Wide World Importers</t>
+        </is>
+      </c>
+      <c r="C91" t="inlineStr">
+        <is>
+          <t>INV-2012</t>
+        </is>
+      </c>
+      <c r="D91" t="n">
+        <v>-6679.81</v>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="inlineStr">
+        <is>
+          <t>02/02/2024</t>
+        </is>
+      </c>
+      <c r="B92" t="inlineStr">
+        <is>
+          <t>Tailspin travel booking Tailspin Travel</t>
+        </is>
+      </c>
+      <c r="C92" t="inlineStr">
+        <is>
+          <t>INV-2088</t>
+        </is>
+      </c>
+      <c r="D92" t="n">
+        <v>-3556.08</v>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="inlineStr">
+        <is>
+          <t>12/04/2024</t>
+        </is>
+      </c>
+      <c r="B93" t="inlineStr">
+        <is>
+          <t>Accrual - goods received not invoiced</t>
+        </is>
+      </c>
+      <c r="C93" t="inlineStr">
+        <is>
+          <t>ACC-9001</t>
+        </is>
+      </c>
+      <c r="D93" t="n">
+        <v>-1860.35</v>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="inlineStr">
+        <is>
+          <t>08/02/2024</t>
+        </is>
+      </c>
+      <c r="B94" t="inlineStr">
+        <is>
+          <t>Contoso Supplies invoice Contoso Supplies</t>
+        </is>
+      </c>
+      <c r="C94" t="inlineStr">
+        <is>
+          <t>INV-2086</t>
+        </is>
+      </c>
+      <c r="D94" t="n">
+        <v>-2820.39</v>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="inlineStr">
+        <is>
+          <t>02/05/2024</t>
+        </is>
+      </c>
+      <c r="B95" t="inlineStr">
+        <is>
+          <t>Proseware legal fees Proseware Legal</t>
+        </is>
+      </c>
+      <c r="C95" t="inlineStr">
+        <is>
+          <t>INV-2004</t>
+        </is>
+      </c>
+      <c r="D95" t="n">
+        <v>-287.53</v>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="inlineStr">
+        <is>
+          <t>18/04/2024</t>
+        </is>
+      </c>
+      <c r="B96" t="inlineStr">
+        <is>
+          <t>Adatum office cleaning Adatum Cleaning</t>
+        </is>
+      </c>
+      <c r="C96" t="inlineStr">
+        <is>
+          <t>INV-2022</t>
+        </is>
+      </c>
+      <c r="D96" t="n">
+        <v>-5779.52</v>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="inlineStr">
+        <is>
+          <t>06/04/2024</t>
+        </is>
+      </c>
+      <c r="B97" t="inlineStr">
+        <is>
+          <t>Litware cloud hosting Litware Hosting</t>
+        </is>
+      </c>
+      <c r="C97" t="inlineStr">
+        <is>
+          <t>INV-2001</t>
+        </is>
+      </c>
+      <c r="D97" t="n">
+        <v>-369.16</v>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="inlineStr">
+        <is>
+          <t>24/03/2024</t>
+        </is>
+      </c>
+      <c r="B98" t="inlineStr">
+        <is>
+          <t>Fourth Coffee pantry Fourth Coffee</t>
+        </is>
+      </c>
+      <c r="C98" t="inlineStr">
+        <is>
+          <t>INV-2071</t>
+        </is>
+      </c>
+      <c r="D98" t="n">
+        <v>-3346.03</v>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="inlineStr">
+        <is>
+          <t>14/04/2024</t>
+        </is>
+      </c>
+      <c r="B99" t="inlineStr">
+        <is>
+          <t>Graphic Design Institute Graphic Design Inst</t>
+        </is>
+      </c>
+      <c r="C99" t="inlineStr">
+        <is>
+          <t>INV-2053</t>
+        </is>
+      </c>
+      <c r="D99" t="n">
+        <v>-470.63</v>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="inlineStr">
+        <is>
+          <t>22/04/2024</t>
+        </is>
+      </c>
+      <c r="B100" t="inlineStr">
+        <is>
+          <t>Graphic Design Institute Graphic Design Inst</t>
+        </is>
+      </c>
+      <c r="C100" t="inlineStr">
+        <is>
+          <t>INV-2046</t>
+        </is>
+      </c>
+      <c r="D100" t="n">
+        <v>-7221.3</v>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="inlineStr">
+        <is>
+          <t>07/01/2024</t>
+        </is>
+      </c>
+      <c r="B101" t="inlineStr">
+        <is>
+          <t>Litware cloud hosting Litware Hosting</t>
+        </is>
+      </c>
+      <c r="C101" t="inlineStr">
+        <is>
+          <t>INV-2089</t>
+        </is>
+      </c>
+      <c r="D101" t="n">
+        <v>-4537.48</v>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" t="inlineStr">
+        <is>
+          <t>12/04/2024</t>
+        </is>
+      </c>
+      <c r="B102" t="inlineStr">
+        <is>
+          <t>Proseware legal fees Proseware Legal</t>
+        </is>
+      </c>
+      <c r="C102" t="inlineStr">
+        <is>
+          <t>INV-5000</t>
+        </is>
+      </c>
+      <c r="D102" t="n">
+        <v>-606.88</v>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" t="inlineStr">
+        <is>
+          <t>23/01/2024</t>
+        </is>
+      </c>
+      <c r="B103" t="inlineStr">
+        <is>
+          <t>Coho Vineyard payment received Coho Vineyard</t>
+        </is>
+      </c>
+      <c r="C103" t="inlineStr">
+        <is>
+          <t>INV-2021</t>
+        </is>
+      </c>
+      <c r="D103" t="n">
+        <v>8352.23</v>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" t="inlineStr">
+        <is>
+          <t>07/01/2024</t>
+        </is>
+      </c>
+      <c r="B104" t="inlineStr">
+        <is>
+          <t>Wide World Importers goods Wide World Importers</t>
+        </is>
+      </c>
+      <c r="C104" t="inlineStr">
+        <is>
+          <t>INV-2087</t>
+        </is>
+      </c>
+      <c r="D104" t="n">
+        <v>-8958.32</v>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" t="inlineStr">
+        <is>
+          <t>08/04/2024</t>
+        </is>
+      </c>
+      <c r="B105" t="inlineStr">
+        <is>
+          <t>Graphic Design Institute Graphic Design Inst</t>
+        </is>
+      </c>
+      <c r="C105" t="inlineStr">
+        <is>
+          <t>INV-2058</t>
+        </is>
+      </c>
+      <c r="D105" t="n">
+        <v>-7234.56</v>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" t="inlineStr">
+        <is>
+          <t>27/03/2024</t>
+        </is>
+      </c>
+      <c r="B106" t="inlineStr">
+        <is>
+          <t>Payment - Northwind Traders Ltd Northwind Traders</t>
+        </is>
+      </c>
+      <c r="C106" t="inlineStr">
+        <is>
+          <t>INV-2032</t>
+        </is>
+      </c>
+      <c r="D106" t="n">
+        <v>-2049.41</v>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" t="inlineStr">
+        <is>
+          <t>11/02/2024</t>
+        </is>
+      </c>
+      <c r="B107" t="inlineStr">
+        <is>
+          <t>Accrual - goods received not invoiced</t>
+        </is>
+      </c>
+      <c r="C107" t="inlineStr">
+        <is>
+          <t>ACC-9002</t>
+        </is>
+      </c>
+      <c r="D107" t="n">
+        <v>-485.69</v>
       </c>
     </row>
   </sheetData>
